--- a/output/Data and Chart Outputs/gb_storage_sites_daily.xlsx
+++ b/output/Data and Chart Outputs/gb_storage_sites_daily.xlsx
@@ -156,6 +156,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>GB gas storage stock by site, month end (National Gas) (to Oct/26)</a:t>
             </a:r>
           </a:p>
@@ -487,6 +488,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>GB gas storage net withdrawal by site (National Gas) (to Sep/26)</a:t>
             </a:r>
           </a:p>
@@ -1217,7 +1219,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-04 14:10 UTC; 1826 days, 2021-10-04 to 2026-10-03</t>
+          <t>2026-10-28 00:39 UTC; 1850 days, 2021-10-04 to 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -2041,25 +2043,25 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>2.77556</v>
+        <v>3.749558</v>
       </c>
       <c r="D28" t="n">
-        <v>2.472332</v>
+        <v>2.727626</v>
       </c>
       <c r="E28" t="n">
-        <v>1.958529</v>
+        <v>2.361605</v>
       </c>
       <c r="F28" t="n">
-        <v>1.283751</v>
+        <v>2.131241</v>
       </c>
       <c r="G28" t="n">
-        <v>0.01932</v>
+        <v>0.598543</v>
       </c>
       <c r="H28" t="n">
-        <v>0.575062</v>
+        <v>0.716778</v>
       </c>
       <c r="I28" t="n">
-        <v>0.269034</v>
+        <v>0.5546340000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2893,7 +2895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1827"/>
+  <dimension ref="A1:AF1851"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86192,6 +86194,2358 @@
         <v>9353.587</v>
       </c>
     </row>
+    <row r="1828">
+      <c r="A1828" s="4" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B1828" t="n">
+        <v>1449.316</v>
+      </c>
+      <c r="C1828" t="n">
+        <v>165.565</v>
+      </c>
+      <c r="D1828" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1828" t="n">
+        <v>588.6079999999999</v>
+      </c>
+      <c r="F1828" t="n">
+        <v>13.547</v>
+      </c>
+      <c r="G1828" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1828" t="n">
+        <v>101.678</v>
+      </c>
+      <c r="I1828" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1828" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1828" t="n">
+        <v>167.356</v>
+      </c>
+      <c r="L1828" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1828" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1828" t="n">
+        <v>1958.529</v>
+      </c>
+      <c r="O1828" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1828" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1828" t="n">
+        <v>2485.824</v>
+      </c>
+      <c r="R1828" t="n">
+        <v>13.492</v>
+      </c>
+      <c r="S1828" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1828" t="n">
+        <v>72.53700000000001</v>
+      </c>
+      <c r="U1828" t="n">
+        <v>53.217</v>
+      </c>
+      <c r="V1828" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1828" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1828" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1828" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z1828" t="n">
+        <v>3016.46</v>
+      </c>
+      <c r="AA1828" t="n">
+        <v>240.9</v>
+      </c>
+      <c r="AB1828" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC1828" t="n">
+        <v>9840.308000000001</v>
+      </c>
+      <c r="AD1828" t="n">
+        <v>486.721</v>
+      </c>
+      <c r="AE1828" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF1828" t="n">
+        <v>9840.308000000001</v>
+      </c>
+    </row>
+    <row r="1829">
+      <c r="A1829" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B1829" t="n">
+        <v>1501.176</v>
+      </c>
+      <c r="C1829" t="n">
+        <v>51.859</v>
+      </c>
+      <c r="D1829" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1829" t="n">
+        <v>602.253</v>
+      </c>
+      <c r="F1829" t="n">
+        <v>13.645</v>
+      </c>
+      <c r="G1829" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1829" t="n">
+        <v>190.055</v>
+      </c>
+      <c r="I1829" t="n">
+        <v>88.378</v>
+      </c>
+      <c r="J1829" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1829" t="n">
+        <v>167.356</v>
+      </c>
+      <c r="L1829" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1829" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1829" t="n">
+        <v>1958.529</v>
+      </c>
+      <c r="O1829" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1829" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1829" t="n">
+        <v>2499.124</v>
+      </c>
+      <c r="R1829" t="n">
+        <v>13.301</v>
+      </c>
+      <c r="S1829" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1829" t="n">
+        <v>133.518</v>
+      </c>
+      <c r="U1829" t="n">
+        <v>60.981</v>
+      </c>
+      <c r="V1829" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1829" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1829" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1829" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z1829" t="n">
+        <v>3280.77</v>
+      </c>
+      <c r="AA1829" t="n">
+        <v>264.31</v>
+      </c>
+      <c r="AB1829" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC1829" t="n">
+        <v>10332.781</v>
+      </c>
+      <c r="AD1829" t="n">
+        <v>492.473</v>
+      </c>
+      <c r="AE1829" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF1829" t="n">
+        <v>10332.781</v>
+      </c>
+    </row>
+    <row r="1830">
+      <c r="A1830" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1830" t="n">
+        <v>1589.388</v>
+      </c>
+      <c r="C1830" t="n">
+        <v>88.21299999999999</v>
+      </c>
+      <c r="D1830" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1830" t="n">
+        <v>611.088</v>
+      </c>
+      <c r="F1830" t="n">
+        <v>8.835000000000001</v>
+      </c>
+      <c r="G1830" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1830" t="n">
+        <v>236.514</v>
+      </c>
+      <c r="I1830" t="n">
+        <v>46.458</v>
+      </c>
+      <c r="J1830" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1830" t="n">
+        <v>167.356</v>
+      </c>
+      <c r="L1830" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1830" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1830" t="n">
+        <v>1958.529</v>
+      </c>
+      <c r="O1830" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1830" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1830" t="n">
+        <v>2510.254</v>
+      </c>
+      <c r="R1830" t="n">
+        <v>11.129</v>
+      </c>
+      <c r="S1830" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1830" t="n">
+        <v>194.485</v>
+      </c>
+      <c r="U1830" t="n">
+        <v>60.967</v>
+      </c>
+      <c r="V1830" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1830" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1830" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1830" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z1830" t="n">
+        <v>3511.138</v>
+      </c>
+      <c r="AA1830" t="n">
+        <v>230.368</v>
+      </c>
+      <c r="AB1830" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC1830" t="n">
+        <v>10778.751</v>
+      </c>
+      <c r="AD1830" t="n">
+        <v>445.97</v>
+      </c>
+      <c r="AE1830" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF1830" t="n">
+        <v>10778.751</v>
+      </c>
+    </row>
+    <row r="1831">
+      <c r="A1831" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B1831" t="n">
+        <v>1449.265</v>
+      </c>
+      <c r="C1831" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1831" t="n">
+        <v>140.124</v>
+      </c>
+      <c r="E1831" t="n">
+        <v>611.088</v>
+      </c>
+      <c r="F1831" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1831" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1831" t="n">
+        <v>214.453</v>
+      </c>
+      <c r="I1831" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1831" t="n">
+        <v>22.061</v>
+      </c>
+      <c r="K1831" t="n">
+        <v>167.356</v>
+      </c>
+      <c r="L1831" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1831" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1831" t="n">
+        <v>1958.529</v>
+      </c>
+      <c r="O1831" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1831" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1831" t="n">
+        <v>2521.928</v>
+      </c>
+      <c r="R1831" t="n">
+        <v>11.674</v>
+      </c>
+      <c r="S1831" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1831" t="n">
+        <v>194.485</v>
+      </c>
+      <c r="U1831" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1831" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1831" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1831" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1831" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z1831" t="n">
+        <v>3572.107</v>
+      </c>
+      <c r="AA1831" t="n">
+        <v>60.97</v>
+      </c>
+      <c r="AB1831" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC1831" t="n">
+        <v>10689.21</v>
+      </c>
+      <c r="AD1831" t="n">
+        <v>72.643</v>
+      </c>
+      <c r="AE1831" t="n">
+        <v>162.185</v>
+      </c>
+      <c r="AF1831" t="n">
+        <v>10689.21</v>
+      </c>
+    </row>
+    <row r="1832">
+      <c r="A1832" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B1832" t="n">
+        <v>1457.426</v>
+      </c>
+      <c r="C1832" t="n">
+        <v>8.161</v>
+      </c>
+      <c r="D1832" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1832" t="n">
+        <v>611.088</v>
+      </c>
+      <c r="F1832" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1832" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1832" t="n">
+        <v>214.453</v>
+      </c>
+      <c r="I1832" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1832" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1832" t="n">
+        <v>167.356</v>
+      </c>
+      <c r="L1832" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1832" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1832" t="n">
+        <v>1958.529</v>
+      </c>
+      <c r="O1832" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1832" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1832" t="n">
+        <v>2533.737</v>
+      </c>
+      <c r="R1832" t="n">
+        <v>11.809</v>
+      </c>
+      <c r="S1832" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1832" t="n">
+        <v>249.449</v>
+      </c>
+      <c r="U1832" t="n">
+        <v>54.965</v>
+      </c>
+      <c r="V1832" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1832" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1832" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1832" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z1832" t="n">
+        <v>3719.1</v>
+      </c>
+      <c r="AA1832" t="n">
+        <v>146.992</v>
+      </c>
+      <c r="AB1832" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC1832" t="n">
+        <v>10911.138</v>
+      </c>
+      <c r="AD1832" t="n">
+        <v>221.928</v>
+      </c>
+      <c r="AE1832" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF1832" t="n">
+        <v>10911.138</v>
+      </c>
+    </row>
+    <row r="1833">
+      <c r="A1833" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B1833" t="n">
+        <v>1453.589</v>
+      </c>
+      <c r="C1833" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1833" t="n">
+        <v>3.837</v>
+      </c>
+      <c r="E1833" t="n">
+        <v>624.308</v>
+      </c>
+      <c r="F1833" t="n">
+        <v>13.219</v>
+      </c>
+      <c r="G1833" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1833" t="n">
+        <v>257.333</v>
+      </c>
+      <c r="I1833" t="n">
+        <v>42.881</v>
+      </c>
+      <c r="J1833" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1833" t="n">
+        <v>167.356</v>
+      </c>
+      <c r="L1833" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1833" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1833" t="n">
+        <v>1958.529</v>
+      </c>
+      <c r="O1833" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1833" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1833" t="n">
+        <v>2545.963</v>
+      </c>
+      <c r="R1833" t="n">
+        <v>12.226</v>
+      </c>
+      <c r="S1833" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1833" t="n">
+        <v>308.53</v>
+      </c>
+      <c r="U1833" t="n">
+        <v>59.081</v>
+      </c>
+      <c r="V1833" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1833" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1833" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1833" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z1833" t="n">
+        <v>3746.881</v>
+      </c>
+      <c r="AA1833" t="n">
+        <v>27.781</v>
+      </c>
+      <c r="AB1833" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC1833" t="n">
+        <v>11062.488</v>
+      </c>
+      <c r="AD1833" t="n">
+        <v>155.188</v>
+      </c>
+      <c r="AE1833" t="n">
+        <v>3.837</v>
+      </c>
+      <c r="AF1833" t="n">
+        <v>11062.488</v>
+      </c>
+    </row>
+    <row r="1834">
+      <c r="A1834" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B1834" t="n">
+        <v>1800.278</v>
+      </c>
+      <c r="C1834" t="n">
+        <v>346.689</v>
+      </c>
+      <c r="D1834" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1834" t="n">
+        <v>641.9</v>
+      </c>
+      <c r="F1834" t="n">
+        <v>17.593</v>
+      </c>
+      <c r="G1834" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1834" t="n">
+        <v>289.772</v>
+      </c>
+      <c r="I1834" t="n">
+        <v>32.439</v>
+      </c>
+      <c r="J1834" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1834" t="n">
+        <v>167.356</v>
+      </c>
+      <c r="L1834" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1834" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1834" t="n">
+        <v>1958.529</v>
+      </c>
+      <c r="O1834" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1834" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1834" t="n">
+        <v>2556.646</v>
+      </c>
+      <c r="R1834" t="n">
+        <v>10.684</v>
+      </c>
+      <c r="S1834" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1834" t="n">
+        <v>367.612</v>
+      </c>
+      <c r="U1834" t="n">
+        <v>59.082</v>
+      </c>
+      <c r="V1834" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1834" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1834" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1834" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z1834" t="n">
+        <v>3882.907</v>
+      </c>
+      <c r="AA1834" t="n">
+        <v>136.026</v>
+      </c>
+      <c r="AB1834" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC1834" t="n">
+        <v>11665</v>
+      </c>
+      <c r="AD1834" t="n">
+        <v>602.5119999999999</v>
+      </c>
+      <c r="AE1834" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF1834" t="n">
+        <v>11665</v>
+      </c>
+    </row>
+    <row r="1835">
+      <c r="A1835" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B1835" t="n">
+        <v>2081.696</v>
+      </c>
+      <c r="C1835" t="n">
+        <v>281.418</v>
+      </c>
+      <c r="D1835" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1835" t="n">
+        <v>659.518</v>
+      </c>
+      <c r="F1835" t="n">
+        <v>17.618</v>
+      </c>
+      <c r="G1835" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1835" t="n">
+        <v>330.25</v>
+      </c>
+      <c r="I1835" t="n">
+        <v>40.478</v>
+      </c>
+      <c r="J1835" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1835" t="n">
+        <v>167.356</v>
+      </c>
+      <c r="L1835" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1835" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1835" t="n">
+        <v>1958.529</v>
+      </c>
+      <c r="O1835" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1835" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1835" t="n">
+        <v>2568.774</v>
+      </c>
+      <c r="R1835" t="n">
+        <v>12.128</v>
+      </c>
+      <c r="S1835" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1835" t="n">
+        <v>367.612</v>
+      </c>
+      <c r="U1835" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1835" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1835" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1835" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1835" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z1835" t="n">
+        <v>4012.795</v>
+      </c>
+      <c r="AA1835" t="n">
+        <v>129.888</v>
+      </c>
+      <c r="AB1835" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC1835" t="n">
+        <v>12146.53</v>
+      </c>
+      <c r="AD1835" t="n">
+        <v>481.529</v>
+      </c>
+      <c r="AE1835" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF1835" t="n">
+        <v>12146.53</v>
+      </c>
+    </row>
+    <row r="1836">
+      <c r="A1836" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B1836" t="n">
+        <v>2027.732</v>
+      </c>
+      <c r="C1836" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1836" t="n">
+        <v>53.964</v>
+      </c>
+      <c r="E1836" t="n">
+        <v>672.744</v>
+      </c>
+      <c r="F1836" t="n">
+        <v>13.226</v>
+      </c>
+      <c r="G1836" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1836" t="n">
+        <v>339.189</v>
+      </c>
+      <c r="I1836" t="n">
+        <v>8.939</v>
+      </c>
+      <c r="J1836" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1836" t="n">
+        <v>167.356</v>
+      </c>
+      <c r="L1836" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1836" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1836" t="n">
+        <v>1958.529</v>
+      </c>
+      <c r="O1836" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1836" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1836" t="n">
+        <v>2583.018</v>
+      </c>
+      <c r="R1836" t="n">
+        <v>14.244</v>
+      </c>
+      <c r="S1836" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1836" t="n">
+        <v>367.612</v>
+      </c>
+      <c r="U1836" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1836" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1836" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1836" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1836" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z1836" t="n">
+        <v>4056.87</v>
+      </c>
+      <c r="AA1836" t="n">
+        <v>44.075</v>
+      </c>
+      <c r="AB1836" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC1836" t="n">
+        <v>12173.05</v>
+      </c>
+      <c r="AD1836" t="n">
+        <v>80.483</v>
+      </c>
+      <c r="AE1836" t="n">
+        <v>53.964</v>
+      </c>
+      <c r="AF1836" t="n">
+        <v>12173.05</v>
+      </c>
+    </row>
+    <row r="1837">
+      <c r="A1837" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B1837" t="n">
+        <v>2082.518</v>
+      </c>
+      <c r="C1837" t="n">
+        <v>54.786</v>
+      </c>
+      <c r="D1837" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1837" t="n">
+        <v>685.944</v>
+      </c>
+      <c r="F1837" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="G1837" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1837" t="n">
+        <v>301.122</v>
+      </c>
+      <c r="I1837" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1837" t="n">
+        <v>38.067</v>
+      </c>
+      <c r="K1837" t="n">
+        <v>167.356</v>
+      </c>
+      <c r="L1837" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1837" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1837" t="n">
+        <v>1958.529</v>
+      </c>
+      <c r="O1837" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1837" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1837" t="n">
+        <v>2596.633</v>
+      </c>
+      <c r="R1837" t="n">
+        <v>13.615</v>
+      </c>
+      <c r="S1837" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1837" t="n">
+        <v>420.398</v>
+      </c>
+      <c r="U1837" t="n">
+        <v>52.786</v>
+      </c>
+      <c r="V1837" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1837" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1837" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1837" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z1837" t="n">
+        <v>4082.354</v>
+      </c>
+      <c r="AA1837" t="n">
+        <v>25.485</v>
+      </c>
+      <c r="AB1837" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC1837" t="n">
+        <v>12294.854</v>
+      </c>
+      <c r="AD1837" t="n">
+        <v>159.871</v>
+      </c>
+      <c r="AE1837" t="n">
+        <v>38.067</v>
+      </c>
+      <c r="AF1837" t="n">
+        <v>12294.854</v>
+      </c>
+    </row>
+    <row r="1838">
+      <c r="A1838" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B1838" t="n">
+        <v>2197.571</v>
+      </c>
+      <c r="C1838" t="n">
+        <v>115.054</v>
+      </c>
+      <c r="D1838" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1838" t="n">
+        <v>703.557</v>
+      </c>
+      <c r="F1838" t="n">
+        <v>17.613</v>
+      </c>
+      <c r="G1838" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1838" t="n">
+        <v>365.903</v>
+      </c>
+      <c r="I1838" t="n">
+        <v>64.78100000000001</v>
+      </c>
+      <c r="J1838" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1838" t="n">
+        <v>167.356</v>
+      </c>
+      <c r="L1838" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1838" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1838" t="n">
+        <v>1958.529</v>
+      </c>
+      <c r="O1838" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1838" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1838" t="n">
+        <v>2610.43</v>
+      </c>
+      <c r="R1838" t="n">
+        <v>13.796</v>
+      </c>
+      <c r="S1838" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1838" t="n">
+        <v>478.508</v>
+      </c>
+      <c r="U1838" t="n">
+        <v>58.11</v>
+      </c>
+      <c r="V1838" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1838" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1838" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1838" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z1838" t="n">
+        <v>4297.035</v>
+      </c>
+      <c r="AA1838" t="n">
+        <v>214.681</v>
+      </c>
+      <c r="AB1838" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC1838" t="n">
+        <v>12778.889</v>
+      </c>
+      <c r="AD1838" t="n">
+        <v>484.035</v>
+      </c>
+      <c r="AE1838" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF1838" t="n">
+        <v>12778.889</v>
+      </c>
+    </row>
+    <row r="1839">
+      <c r="A1839" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B1839" t="n">
+        <v>2267.597</v>
+      </c>
+      <c r="C1839" t="n">
+        <v>70.026</v>
+      </c>
+      <c r="D1839" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1839" t="n">
+        <v>703.557</v>
+      </c>
+      <c r="F1839" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1839" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1839" t="n">
+        <v>402.114</v>
+      </c>
+      <c r="I1839" t="n">
+        <v>36.211</v>
+      </c>
+      <c r="J1839" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1839" t="n">
+        <v>167.356</v>
+      </c>
+      <c r="L1839" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1839" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1839" t="n">
+        <v>1958.693</v>
+      </c>
+      <c r="O1839" t="n">
+        <v>0.164</v>
+      </c>
+      <c r="P1839" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1839" t="n">
+        <v>2623.589</v>
+      </c>
+      <c r="R1839" t="n">
+        <v>13.159</v>
+      </c>
+      <c r="S1839" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1839" t="n">
+        <v>538.546</v>
+      </c>
+      <c r="U1839" t="n">
+        <v>60.038</v>
+      </c>
+      <c r="V1839" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1839" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1839" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1839" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z1839" t="n">
+        <v>4379.153</v>
+      </c>
+      <c r="AA1839" t="n">
+        <v>82.11799999999999</v>
+      </c>
+      <c r="AB1839" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC1839" t="n">
+        <v>13040.605</v>
+      </c>
+      <c r="AD1839" t="n">
+        <v>261.716</v>
+      </c>
+      <c r="AE1839" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF1839" t="n">
+        <v>13040.605</v>
+      </c>
+    </row>
+    <row r="1840">
+      <c r="A1840" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B1840" t="n">
+        <v>2307.699</v>
+      </c>
+      <c r="C1840" t="n">
+        <v>40.102</v>
+      </c>
+      <c r="D1840" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1840" t="n">
+        <v>716.7809999999999</v>
+      </c>
+      <c r="F1840" t="n">
+        <v>13.224</v>
+      </c>
+      <c r="G1840" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1840" t="n">
+        <v>454.294</v>
+      </c>
+      <c r="I1840" t="n">
+        <v>52.181</v>
+      </c>
+      <c r="J1840" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1840" t="n">
+        <v>167.356</v>
+      </c>
+      <c r="L1840" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1840" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1840" t="n">
+        <v>2037.807</v>
+      </c>
+      <c r="O1840" t="n">
+        <v>79.114</v>
+      </c>
+      <c r="P1840" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1840" t="n">
+        <v>2637.314</v>
+      </c>
+      <c r="R1840" t="n">
+        <v>13.725</v>
+      </c>
+      <c r="S1840" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1840" t="n">
+        <v>598.543</v>
+      </c>
+      <c r="U1840" t="n">
+        <v>59.997</v>
+      </c>
+      <c r="V1840" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1840" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1840" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1840" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z1840" t="n">
+        <v>4376.175</v>
+      </c>
+      <c r="AA1840" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB1840" t="n">
+        <v>2.978</v>
+      </c>
+      <c r="AC1840" t="n">
+        <v>13295.969</v>
+      </c>
+      <c r="AD1840" t="n">
+        <v>258.342</v>
+      </c>
+      <c r="AE1840" t="n">
+        <v>2.978</v>
+      </c>
+      <c r="AF1840" t="n">
+        <v>13295.969</v>
+      </c>
+    </row>
+    <row r="1841">
+      <c r="A1841" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B1841" t="n">
+        <v>2376.947</v>
+      </c>
+      <c r="C1841" t="n">
+        <v>69.247</v>
+      </c>
+      <c r="D1841" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1841" t="n">
+        <v>716.7809999999999</v>
+      </c>
+      <c r="F1841" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1841" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1841" t="n">
+        <v>454.294</v>
+      </c>
+      <c r="I1841" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1841" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1841" t="n">
+        <v>167.356</v>
+      </c>
+      <c r="L1841" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1841" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1841" t="n">
+        <v>2161.46</v>
+      </c>
+      <c r="O1841" t="n">
+        <v>123.653</v>
+      </c>
+      <c r="P1841" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1841" t="n">
+        <v>2651.042</v>
+      </c>
+      <c r="R1841" t="n">
+        <v>13.728</v>
+      </c>
+      <c r="S1841" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1841" t="n">
+        <v>598.543</v>
+      </c>
+      <c r="U1841" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1841" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1841" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1841" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1841" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z1841" t="n">
+        <v>4417.21</v>
+      </c>
+      <c r="AA1841" t="n">
+        <v>41.035</v>
+      </c>
+      <c r="AB1841" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC1841" t="n">
+        <v>13543.633</v>
+      </c>
+      <c r="AD1841" t="n">
+        <v>247.664</v>
+      </c>
+      <c r="AE1841" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF1841" t="n">
+        <v>13543.633</v>
+      </c>
+    </row>
+    <row r="1842">
+      <c r="A1842" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B1842" t="n">
+        <v>2393.845</v>
+      </c>
+      <c r="C1842" t="n">
+        <v>16.898</v>
+      </c>
+      <c r="D1842" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1842" t="n">
+        <v>716.7809999999999</v>
+      </c>
+      <c r="F1842" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1842" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1842" t="n">
+        <v>531.675</v>
+      </c>
+      <c r="I1842" t="n">
+        <v>77.381</v>
+      </c>
+      <c r="J1842" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1842" t="n">
+        <v>167.356</v>
+      </c>
+      <c r="L1842" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1842" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1842" t="n">
+        <v>2222.389</v>
+      </c>
+      <c r="O1842" t="n">
+        <v>60.928</v>
+      </c>
+      <c r="P1842" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1842" t="n">
+        <v>2664.597</v>
+      </c>
+      <c r="R1842" t="n">
+        <v>13.555</v>
+      </c>
+      <c r="S1842" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1842" t="n">
+        <v>598.543</v>
+      </c>
+      <c r="U1842" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1842" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1842" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1842" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1842" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z1842" t="n">
+        <v>4513.018</v>
+      </c>
+      <c r="AA1842" t="n">
+        <v>95.80800000000001</v>
+      </c>
+      <c r="AB1842" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC1842" t="n">
+        <v>13808.203</v>
+      </c>
+      <c r="AD1842" t="n">
+        <v>264.57</v>
+      </c>
+      <c r="AE1842" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF1842" t="n">
+        <v>13808.203</v>
+      </c>
+    </row>
+    <row r="1843">
+      <c r="A1843" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B1843" t="n">
+        <v>2370.391</v>
+      </c>
+      <c r="C1843" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1843" t="n">
+        <v>23.454</v>
+      </c>
+      <c r="E1843" t="n">
+        <v>716.7809999999999</v>
+      </c>
+      <c r="F1843" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1843" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1843" t="n">
+        <v>580.236</v>
+      </c>
+      <c r="I1843" t="n">
+        <v>48.561</v>
+      </c>
+      <c r="J1843" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1843" t="n">
+        <v>167.356</v>
+      </c>
+      <c r="L1843" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1843" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1843" t="n">
+        <v>2246.552</v>
+      </c>
+      <c r="O1843" t="n">
+        <v>24.164</v>
+      </c>
+      <c r="P1843" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1843" t="n">
+        <v>2677.066</v>
+      </c>
+      <c r="R1843" t="n">
+        <v>12.469</v>
+      </c>
+      <c r="S1843" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1843" t="n">
+        <v>598.543</v>
+      </c>
+      <c r="U1843" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1843" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1843" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1843" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1843" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z1843" t="n">
+        <v>4489.704</v>
+      </c>
+      <c r="AA1843" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB1843" t="n">
+        <v>23.314</v>
+      </c>
+      <c r="AC1843" t="n">
+        <v>13846.628</v>
+      </c>
+      <c r="AD1843" t="n">
+        <v>85.194</v>
+      </c>
+      <c r="AE1843" t="n">
+        <v>46.769</v>
+      </c>
+      <c r="AF1843" t="n">
+        <v>13846.628</v>
+      </c>
+    </row>
+    <row r="1844">
+      <c r="A1844" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B1844" t="n">
+        <v>2336.029</v>
+      </c>
+      <c r="C1844" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1844" t="n">
+        <v>34.362</v>
+      </c>
+      <c r="E1844" t="n">
+        <v>716.778</v>
+      </c>
+      <c r="F1844" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1844" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H1844" t="n">
+        <v>562.516</v>
+      </c>
+      <c r="I1844" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1844" t="n">
+        <v>17.719</v>
+      </c>
+      <c r="K1844" t="n">
+        <v>167.356</v>
+      </c>
+      <c r="L1844" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1844" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1844" t="n">
+        <v>2246.552</v>
+      </c>
+      <c r="O1844" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1844" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1844" t="n">
+        <v>2689.156</v>
+      </c>
+      <c r="R1844" t="n">
+        <v>12.09</v>
+      </c>
+      <c r="S1844" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1844" t="n">
+        <v>598.543</v>
+      </c>
+      <c r="U1844" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1844" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1844" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1844" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1844" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z1844" t="n">
+        <v>4367.358</v>
+      </c>
+      <c r="AA1844" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB1844" t="n">
+        <v>122.346</v>
+      </c>
+      <c r="AC1844" t="n">
+        <v>13684.288</v>
+      </c>
+      <c r="AD1844" t="n">
+        <v>12.09</v>
+      </c>
+      <c r="AE1844" t="n">
+        <v>174.43</v>
+      </c>
+      <c r="AF1844" t="n">
+        <v>13684.288</v>
+      </c>
+    </row>
+    <row r="1845">
+      <c r="A1845" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B1845" t="n">
+        <v>2335.393</v>
+      </c>
+      <c r="C1845" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1845" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E1845" t="n">
+        <v>716.778</v>
+      </c>
+      <c r="F1845" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1845" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1845" t="n">
+        <v>562.516</v>
+      </c>
+      <c r="I1845" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1845" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1845" t="n">
+        <v>167.356</v>
+      </c>
+      <c r="L1845" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1845" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1845" t="n">
+        <v>2246.552</v>
+      </c>
+      <c r="O1845" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1845" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1845" t="n">
+        <v>2701.798</v>
+      </c>
+      <c r="R1845" t="n">
+        <v>12.642</v>
+      </c>
+      <c r="S1845" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1845" t="n">
+        <v>598.543</v>
+      </c>
+      <c r="U1845" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1845" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1845" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1845" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1845" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z1845" t="n">
+        <v>4266.979</v>
+      </c>
+      <c r="AA1845" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB1845" t="n">
+        <v>100.378</v>
+      </c>
+      <c r="AC1845" t="n">
+        <v>13595.916</v>
+      </c>
+      <c r="AD1845" t="n">
+        <v>12.642</v>
+      </c>
+      <c r="AE1845" t="n">
+        <v>101.014</v>
+      </c>
+      <c r="AF1845" t="n">
+        <v>13595.916</v>
+      </c>
+    </row>
+    <row r="1846">
+      <c r="A1846" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B1846" t="n">
+        <v>2315.137</v>
+      </c>
+      <c r="C1846" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1846" t="n">
+        <v>20.256</v>
+      </c>
+      <c r="E1846" t="n">
+        <v>716.778</v>
+      </c>
+      <c r="F1846" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1846" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1846" t="n">
+        <v>562.516</v>
+      </c>
+      <c r="I1846" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1846" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1846" t="n">
+        <v>167.356</v>
+      </c>
+      <c r="L1846" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1846" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1846" t="n">
+        <v>2246.552</v>
+      </c>
+      <c r="O1846" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1846" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1846" t="n">
+        <v>2714.051</v>
+      </c>
+      <c r="R1846" t="n">
+        <v>12.253</v>
+      </c>
+      <c r="S1846" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1846" t="n">
+        <v>598.543</v>
+      </c>
+      <c r="U1846" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1846" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1846" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1846" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1846" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z1846" t="n">
+        <v>4119.574</v>
+      </c>
+      <c r="AA1846" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB1846" t="n">
+        <v>147.405</v>
+      </c>
+      <c r="AC1846" t="n">
+        <v>13440.508</v>
+      </c>
+      <c r="AD1846" t="n">
+        <v>12.253</v>
+      </c>
+      <c r="AE1846" t="n">
+        <v>167.661</v>
+      </c>
+      <c r="AF1846" t="n">
+        <v>13440.508</v>
+      </c>
+    </row>
+    <row r="1847">
+      <c r="A1847" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B1847" t="n">
+        <v>2306.486</v>
+      </c>
+      <c r="C1847" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1847" t="n">
+        <v>8.651</v>
+      </c>
+      <c r="E1847" t="n">
+        <v>716.778</v>
+      </c>
+      <c r="F1847" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1847" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1847" t="n">
+        <v>533.0940000000001</v>
+      </c>
+      <c r="I1847" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1847" t="n">
+        <v>29.422</v>
+      </c>
+      <c r="K1847" t="n">
+        <v>167.356</v>
+      </c>
+      <c r="L1847" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1847" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1847" t="n">
+        <v>2246.552</v>
+      </c>
+      <c r="O1847" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1847" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1847" t="n">
+        <v>2726.569</v>
+      </c>
+      <c r="R1847" t="n">
+        <v>12.518</v>
+      </c>
+      <c r="S1847" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1847" t="n">
+        <v>598.543</v>
+      </c>
+      <c r="U1847" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1847" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1847" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1847" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1847" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z1847" t="n">
+        <v>3923.386</v>
+      </c>
+      <c r="AA1847" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB1847" t="n">
+        <v>196.188</v>
+      </c>
+      <c r="AC1847" t="n">
+        <v>13218.764</v>
+      </c>
+      <c r="AD1847" t="n">
+        <v>12.518</v>
+      </c>
+      <c r="AE1847" t="n">
+        <v>234.261</v>
+      </c>
+      <c r="AF1847" t="n">
+        <v>13218.764</v>
+      </c>
+    </row>
+    <row r="1848">
+      <c r="A1848" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B1848" t="n">
+        <v>2273.053</v>
+      </c>
+      <c r="C1848" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1848" t="n">
+        <v>33.433</v>
+      </c>
+      <c r="E1848" t="n">
+        <v>716.778</v>
+      </c>
+      <c r="F1848" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1848" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1848" t="n">
+        <v>513.466</v>
+      </c>
+      <c r="I1848" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1848" t="n">
+        <v>19.628</v>
+      </c>
+      <c r="K1848" t="n">
+        <v>167.356</v>
+      </c>
+      <c r="L1848" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1848" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1848" t="n">
+        <v>2246.552</v>
+      </c>
+      <c r="O1848" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1848" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1848" t="n">
+        <v>2733.156</v>
+      </c>
+      <c r="R1848" t="n">
+        <v>6.587</v>
+      </c>
+      <c r="S1848" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1848" t="n">
+        <v>598.543</v>
+      </c>
+      <c r="U1848" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1848" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1848" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1848" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1848" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z1848" t="n">
+        <v>3849.654</v>
+      </c>
+      <c r="AA1848" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB1848" t="n">
+        <v>73.732</v>
+      </c>
+      <c r="AC1848" t="n">
+        <v>13098.558</v>
+      </c>
+      <c r="AD1848" t="n">
+        <v>6.587</v>
+      </c>
+      <c r="AE1848" t="n">
+        <v>126.793</v>
+      </c>
+      <c r="AF1848" t="n">
+        <v>13098.558</v>
+      </c>
+    </row>
+    <row r="1849">
+      <c r="A1849" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B1849" t="n">
+        <v>2178.359</v>
+      </c>
+      <c r="C1849" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1849" t="n">
+        <v>94.693</v>
+      </c>
+      <c r="E1849" t="n">
+        <v>716.778</v>
+      </c>
+      <c r="F1849" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1849" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1849" t="n">
+        <v>465.644</v>
+      </c>
+      <c r="I1849" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1849" t="n">
+        <v>47.822</v>
+      </c>
+      <c r="K1849" t="n">
+        <v>167.356</v>
+      </c>
+      <c r="L1849" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1849" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1849" t="n">
+        <v>2299.197</v>
+      </c>
+      <c r="O1849" t="n">
+        <v>52.645</v>
+      </c>
+      <c r="P1849" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1849" t="n">
+        <v>2717.919</v>
+      </c>
+      <c r="R1849" t="n">
+        <v>0</v>
+      </c>
+      <c r="S1849" t="n">
+        <v>15.237</v>
+      </c>
+      <c r="T1849" t="n">
+        <v>598.543</v>
+      </c>
+      <c r="U1849" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1849" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1849" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1849" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1849" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z1849" t="n">
+        <v>3809.516</v>
+      </c>
+      <c r="AA1849" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB1849" t="n">
+        <v>40.138</v>
+      </c>
+      <c r="AC1849" t="n">
+        <v>12953.313</v>
+      </c>
+      <c r="AD1849" t="n">
+        <v>52.645</v>
+      </c>
+      <c r="AE1849" t="n">
+        <v>197.89</v>
+      </c>
+      <c r="AF1849" t="n">
+        <v>12953.313</v>
+      </c>
+    </row>
+    <row r="1850">
+      <c r="A1850" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B1850" t="n">
+        <v>2142.921</v>
+      </c>
+      <c r="C1850" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1850" t="n">
+        <v>35.439</v>
+      </c>
+      <c r="E1850" t="n">
+        <v>716.778</v>
+      </c>
+      <c r="F1850" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1850" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1850" t="n">
+        <v>399.061</v>
+      </c>
+      <c r="I1850" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1850" t="n">
+        <v>66.583</v>
+      </c>
+      <c r="K1850" t="n">
+        <v>167.356</v>
+      </c>
+      <c r="L1850" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1850" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1850" t="n">
+        <v>2335.217</v>
+      </c>
+      <c r="O1850" t="n">
+        <v>36.019</v>
+      </c>
+      <c r="P1850" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1850" t="n">
+        <v>2721.186</v>
+      </c>
+      <c r="R1850" t="n">
+        <v>3.267</v>
+      </c>
+      <c r="S1850" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1850" t="n">
+        <v>598.543</v>
+      </c>
+      <c r="U1850" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1850" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1850" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1850" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1850" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z1850" t="n">
+        <v>3810.985</v>
+      </c>
+      <c r="AA1850" t="n">
+        <v>1.468</v>
+      </c>
+      <c r="AB1850" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC1850" t="n">
+        <v>12892.047</v>
+      </c>
+      <c r="AD1850" t="n">
+        <v>40.755</v>
+      </c>
+      <c r="AE1850" t="n">
+        <v>102.022</v>
+      </c>
+      <c r="AF1850" t="n">
+        <v>12892.047</v>
+      </c>
+    </row>
+    <row r="1851">
+      <c r="A1851" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1851" t="n">
+        <v>2131.241</v>
+      </c>
+      <c r="C1851" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1851" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="E1851" t="n">
+        <v>716.778</v>
+      </c>
+      <c r="F1851" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1851" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1851" t="n">
+        <v>387.278</v>
+      </c>
+      <c r="I1851" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1851" t="n">
+        <v>11.783</v>
+      </c>
+      <c r="K1851" t="n">
+        <v>167.356</v>
+      </c>
+      <c r="L1851" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1851" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1851" t="n">
+        <v>2361.605</v>
+      </c>
+      <c r="O1851" t="n">
+        <v>26.388</v>
+      </c>
+      <c r="P1851" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1851" t="n">
+        <v>2727.626</v>
+      </c>
+      <c r="R1851" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="S1851" t="n">
+        <v>0</v>
+      </c>
+      <c r="T1851" t="n">
+        <v>598.543</v>
+      </c>
+      <c r="U1851" t="n">
+        <v>0</v>
+      </c>
+      <c r="V1851" t="n">
+        <v>0</v>
+      </c>
+      <c r="W1851" t="n">
+        <v>0</v>
+      </c>
+      <c r="X1851" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y1851" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z1851" t="n">
+        <v>3749.558</v>
+      </c>
+      <c r="AA1851" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB1851" t="n">
+        <v>61.427</v>
+      </c>
+      <c r="AC1851" t="n">
+        <v>12839.985</v>
+      </c>
+      <c r="AD1851" t="n">
+        <v>32.828</v>
+      </c>
+      <c r="AE1851" t="n">
+        <v>84.89</v>
+      </c>
+      <c r="AF1851" t="n">
+        <v>12839.985</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
